--- a/frontend/public/Saudi_Template.xlsx
+++ b/frontend/public/Saudi_Template.xlsx
@@ -51,9 +51,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -427,7 +430,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,29 +438,24 @@
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -738,7 +735,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
@@ -862,7 +859,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">    EBITDA</t>
         </is>
@@ -876,21 +873,28 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EBIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Comprehensive Income</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t xml:space="preserve">    Other Comprehensive Income</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Comprehensive Income</t>
         </is>
@@ -907,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -915,7 +919,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,29 +927,24 @@
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1606,7 +1604,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1615,29 +1612,24 @@
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>

--- a/frontend/public/Saudi_Template.xlsx
+++ b/frontend/public/Saudi_Template.xlsx
@@ -440,22 +440,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -929,22 +929,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1614,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
